--- a/4-DataFrames_ready/tsbf_2026.xlsx
+++ b/4-DataFrames_ready/tsbf_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\AI4SH\4-DataFrames_ready\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF595AE-B10F-4A4A-828A-F814155DCF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5303434-8207-40DF-ABC7-0D50EA48BD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3165" yWindow="4665" windowWidth="28800" windowHeight="15540" xr2:uid="{BEF2E00A-38A1-498E-A3FC-273F25E88673}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="29">
   <si>
     <t>horizon</t>
   </si>
@@ -111,15 +111,6 @@
     <t>diplopoda</t>
   </si>
   <si>
-    <t>coleoptera_adult</t>
-  </si>
-  <si>
-    <t>coleoptera_larvae</t>
-  </si>
-  <si>
-    <t>ant</t>
-  </si>
-  <si>
     <t>symphyla</t>
   </si>
   <si>
@@ -127,6 +118,12 @@
   </si>
   <si>
     <t>forest</t>
+  </si>
+  <si>
+    <t>ants</t>
+  </si>
+  <si>
+    <t>coleoptera</t>
   </si>
 </sst>
 </file>
@@ -608,7 +605,7 @@
         <v>46120</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -646,7 +643,7 @@
         <v>46120</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -684,7 +681,7 @@
         <v>46120</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -722,7 +719,7 @@
         <v>46120</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -760,7 +757,7 @@
         <v>46120</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -798,7 +795,7 @@
         <v>46120</v>
       </c>
       <c r="L7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -836,7 +833,7 @@
         <v>46120</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -874,7 +871,7 @@
         <v>46120</v>
       </c>
       <c r="L9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -912,7 +909,7 @@
         <v>46120</v>
       </c>
       <c r="L10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -950,7 +947,7 @@
         <v>46120</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -988,7 +985,7 @@
         <v>46120</v>
       </c>
       <c r="L12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1026,7 +1023,7 @@
         <v>46120</v>
       </c>
       <c r="L13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1064,7 +1061,7 @@
         <v>46120</v>
       </c>
       <c r="L14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1102,7 +1099,7 @@
         <v>46120</v>
       </c>
       <c r="L15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1140,7 +1137,7 @@
         <v>46120</v>
       </c>
       <c r="L16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1178,7 +1175,7 @@
         <v>46120</v>
       </c>
       <c r="L17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1216,7 +1213,7 @@
         <v>46120</v>
       </c>
       <c r="L18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1254,7 +1251,7 @@
         <v>46120</v>
       </c>
       <c r="L19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1292,7 +1289,7 @@
         <v>46120</v>
       </c>
       <c r="L20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1330,7 +1327,7 @@
         <v>46120</v>
       </c>
       <c r="L21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1368,7 +1365,7 @@
         <v>46120</v>
       </c>
       <c r="L22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1406,7 +1403,7 @@
         <v>46120</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1444,7 +1441,7 @@
         <v>46120</v>
       </c>
       <c r="L24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1482,7 +1479,7 @@
         <v>46120</v>
       </c>
       <c r="L25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1520,7 +1517,7 @@
         <v>46120</v>
       </c>
       <c r="L26" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1558,7 +1555,7 @@
         <v>46120</v>
       </c>
       <c r="L27" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1596,7 +1593,7 @@
         <v>46120</v>
       </c>
       <c r="L28" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1634,7 +1631,7 @@
         <v>46120</v>
       </c>
       <c r="L29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1672,7 +1669,7 @@
         <v>46120</v>
       </c>
       <c r="L30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1710,7 +1707,7 @@
         <v>46120</v>
       </c>
       <c r="L31" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1748,7 +1745,7 @@
         <v>46120</v>
       </c>
       <c r="L32" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1786,7 +1783,7 @@
         <v>46120</v>
       </c>
       <c r="L33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1824,7 +1821,7 @@
         <v>46120</v>
       </c>
       <c r="L34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1862,7 +1859,7 @@
         <v>46120</v>
       </c>
       <c r="L35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1900,7 +1897,7 @@
         <v>46120</v>
       </c>
       <c r="L36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1938,7 +1935,7 @@
         <v>46120</v>
       </c>
       <c r="L37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -1976,7 +1973,7 @@
         <v>46120</v>
       </c>
       <c r="L38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2014,7 +2011,7 @@
         <v>46120</v>
       </c>
       <c r="L39" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2052,7 +2049,7 @@
         <v>46120</v>
       </c>
       <c r="L40" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2090,7 +2087,7 @@
         <v>46120</v>
       </c>
       <c r="L41" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2128,7 +2125,7 @@
         <v>46120</v>
       </c>
       <c r="L42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2166,7 +2163,7 @@
         <v>46120</v>
       </c>
       <c r="L43" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2204,7 +2201,7 @@
         <v>46120</v>
       </c>
       <c r="L44" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2242,7 +2239,7 @@
         <v>46120</v>
       </c>
       <c r="L45" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2280,7 +2277,7 @@
         <v>46120</v>
       </c>
       <c r="L46" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2318,7 +2315,7 @@
         <v>46120</v>
       </c>
       <c r="L47" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2356,7 +2353,7 @@
         <v>46120</v>
       </c>
       <c r="L48" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2394,7 +2391,7 @@
         <v>46120</v>
       </c>
       <c r="L49" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2432,7 +2429,7 @@
         <v>46120</v>
       </c>
       <c r="L50" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2470,7 +2467,7 @@
         <v>46120</v>
       </c>
       <c r="L51" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2508,7 +2505,7 @@
         <v>46120</v>
       </c>
       <c r="L52" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2546,7 +2543,7 @@
         <v>46120</v>
       </c>
       <c r="L53" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2584,7 +2581,7 @@
         <v>46120</v>
       </c>
       <c r="L54" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2622,7 +2619,7 @@
         <v>46120</v>
       </c>
       <c r="L55" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2660,7 +2657,7 @@
         <v>46120</v>
       </c>
       <c r="L56" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -2698,7 +2695,7 @@
         <v>46120</v>
       </c>
       <c r="L57" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -2736,7 +2733,7 @@
         <v>46120</v>
       </c>
       <c r="L58" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -2774,7 +2771,7 @@
         <v>46120</v>
       </c>
       <c r="L59" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -2812,7 +2809,7 @@
         <v>46120</v>
       </c>
       <c r="L60" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -2850,7 +2847,7 @@
         <v>46120</v>
       </c>
       <c r="L61" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -2888,7 +2885,7 @@
         <v>46120</v>
       </c>
       <c r="L62" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -2926,7 +2923,7 @@
         <v>46120</v>
       </c>
       <c r="L63" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -2949,7 +2946,7 @@
         <v>16</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -2964,7 +2961,7 @@
         <v>46120</v>
       </c>
       <c r="L64" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -2987,7 +2984,7 @@
         <v>16</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
@@ -3002,7 +2999,7 @@
         <v>46120</v>
       </c>
       <c r="L65" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3025,7 +3022,7 @@
         <v>16</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -3040,7 +3037,7 @@
         <v>46120</v>
       </c>
       <c r="L66" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3063,7 +3060,7 @@
         <v>16</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -3078,7 +3075,7 @@
         <v>46120</v>
       </c>
       <c r="L67" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3101,7 +3098,7 @@
         <v>16</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H68" t="s">
         <v>16</v>
@@ -3116,7 +3113,7 @@
         <v>46120</v>
       </c>
       <c r="L68" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3139,7 +3136,7 @@
         <v>16</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H69" t="s">
         <v>16</v>
@@ -3154,7 +3151,7 @@
         <v>46120</v>
       </c>
       <c r="L69" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3177,7 +3174,7 @@
         <v>16</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
@@ -3192,7 +3189,7 @@
         <v>46120</v>
       </c>
       <c r="L70" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3215,7 +3212,7 @@
         <v>16</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -3230,7 +3227,7 @@
         <v>46120</v>
       </c>
       <c r="L71" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3253,7 +3250,7 @@
         <v>16</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H72" t="s">
         <v>16</v>
@@ -3268,7 +3265,7 @@
         <v>46120</v>
       </c>
       <c r="L72" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3291,7 +3288,7 @@
         <v>16</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H73" t="s">
         <v>16</v>
@@ -3306,7 +3303,7 @@
         <v>46120</v>
       </c>
       <c r="L73" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3344,7 +3341,7 @@
         <v>46120</v>
       </c>
       <c r="L74" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3355,7 +3352,7 @@
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D75" t="s">
         <v>16</v>
@@ -3382,7 +3379,7 @@
         <v>46120</v>
       </c>
       <c r="L75" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3393,7 +3390,7 @@
         <v>20</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D76" t="s">
         <v>16</v>
@@ -3420,7 +3417,7 @@
         <v>46120</v>
       </c>
       <c r="L76" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3431,7 +3428,7 @@
         <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D77" t="s">
         <v>16</v>
@@ -3458,7 +3455,7 @@
         <v>46120</v>
       </c>
       <c r="L77" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3469,7 +3466,7 @@
         <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D78" t="s">
         <v>16</v>
@@ -3496,7 +3493,7 @@
         <v>46120</v>
       </c>
       <c r="L78" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3507,7 +3504,7 @@
         <v>20</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
         <v>16</v>
@@ -3534,7 +3531,7 @@
         <v>46120</v>
       </c>
       <c r="L79" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3545,7 +3542,7 @@
         <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D80" t="s">
         <v>16</v>
@@ -3572,7 +3569,7 @@
         <v>46120</v>
       </c>
       <c r="L80" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3583,7 +3580,7 @@
         <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D81" t="s">
         <v>16</v>
@@ -3610,7 +3607,7 @@
         <v>46120</v>
       </c>
       <c r="L81" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3621,7 +3618,7 @@
         <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D82" t="s">
         <v>16</v>
@@ -3648,7 +3645,7 @@
         <v>46120</v>
       </c>
       <c r="L82" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3659,7 +3656,7 @@
         <v>20</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D83" t="s">
         <v>16</v>
@@ -3686,7 +3683,7 @@
         <v>46120</v>
       </c>
       <c r="L83" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3697,7 +3694,7 @@
         <v>20</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D84" t="s">
         <v>16</v>
@@ -3724,7 +3721,7 @@
         <v>46120</v>
       </c>
       <c r="L84" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3735,7 +3732,7 @@
         <v>20</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D85" t="s">
         <v>16</v>
@@ -3762,7 +3759,7 @@
         <v>46120</v>
       </c>
       <c r="L85" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -3773,7 +3770,7 @@
         <v>20</v>
       </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D86" t="s">
         <v>16</v>
@@ -3800,7 +3797,7 @@
         <v>46120</v>
       </c>
       <c r="L86" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -3811,7 +3808,7 @@
         <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D87" t="s">
         <v>16</v>
@@ -3838,7 +3835,7 @@
         <v>46120</v>
       </c>
       <c r="L87" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -3849,7 +3846,7 @@
         <v>20</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D88" t="s">
         <v>16</v>
@@ -3876,7 +3873,7 @@
         <v>46120</v>
       </c>
       <c r="L88" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -3887,7 +3884,7 @@
         <v>20</v>
       </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D89" t="s">
         <v>16</v>
@@ -3914,7 +3911,7 @@
         <v>46120</v>
       </c>
       <c r="L89" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -3925,7 +3922,7 @@
         <v>20</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D90" t="s">
         <v>16</v>
@@ -3952,7 +3949,7 @@
         <v>46120</v>
       </c>
       <c r="L90" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -3963,7 +3960,7 @@
         <v>20</v>
       </c>
       <c r="C91" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D91" t="s">
         <v>16</v>
@@ -3990,7 +3987,7 @@
         <v>46120</v>
       </c>
       <c r="L91" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4001,7 +3998,7 @@
         <v>20</v>
       </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D92" t="s">
         <v>16</v>
@@ -4028,7 +4025,7 @@
         <v>46120</v>
       </c>
       <c r="L92" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4039,7 +4036,7 @@
         <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D93" t="s">
         <v>16</v>
@@ -4066,7 +4063,7 @@
         <v>46120</v>
       </c>
       <c r="L93" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4077,7 +4074,7 @@
         <v>20</v>
       </c>
       <c r="C94" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D94" t="s">
         <v>16</v>
@@ -4104,7 +4101,7 @@
         <v>46120</v>
       </c>
       <c r="L94" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4115,7 +4112,7 @@
         <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D95" t="s">
         <v>16</v>
@@ -4142,7 +4139,7 @@
         <v>46120</v>
       </c>
       <c r="L95" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4153,7 +4150,7 @@
         <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D96" t="s">
         <v>16</v>
@@ -4180,7 +4177,7 @@
         <v>46120</v>
       </c>
       <c r="L96" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4191,7 +4188,7 @@
         <v>20</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D97" t="s">
         <v>16</v>
@@ -4218,7 +4215,7 @@
         <v>46120</v>
       </c>
       <c r="L97" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4229,7 +4226,7 @@
         <v>20</v>
       </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D98" t="s">
         <v>16</v>
@@ -4256,7 +4253,7 @@
         <v>46120</v>
       </c>
       <c r="L98" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4267,7 +4264,7 @@
         <v>20</v>
       </c>
       <c r="C99" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D99" t="s">
         <v>16</v>
@@ -4294,7 +4291,7 @@
         <v>46120</v>
       </c>
       <c r="L99" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4305,7 +4302,7 @@
         <v>20</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D100" t="s">
         <v>16</v>
@@ -4332,7 +4329,7 @@
         <v>46120</v>
       </c>
       <c r="L100" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4343,7 +4340,7 @@
         <v>20</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D101" t="s">
         <v>16</v>
@@ -4370,7 +4367,7 @@
         <v>46120</v>
       </c>
       <c r="L101" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4381,7 +4378,7 @@
         <v>20</v>
       </c>
       <c r="C102" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D102" t="s">
         <v>16</v>
@@ -4408,7 +4405,7 @@
         <v>46120</v>
       </c>
       <c r="L102" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4419,7 +4416,7 @@
         <v>20</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D103" t="s">
         <v>16</v>
@@ -4446,7 +4443,7 @@
         <v>46120</v>
       </c>
       <c r="L103" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4457,7 +4454,7 @@
         <v>20</v>
       </c>
       <c r="C104" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D104" t="s">
         <v>16</v>
@@ -4484,7 +4481,7 @@
         <v>46120</v>
       </c>
       <c r="L104" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4495,7 +4492,7 @@
         <v>20</v>
       </c>
       <c r="C105" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D105" t="s">
         <v>16</v>
@@ -4522,7 +4519,7 @@
         <v>46120</v>
       </c>
       <c r="L105" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4533,7 +4530,7 @@
         <v>20</v>
       </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
@@ -4560,7 +4557,7 @@
         <v>46120</v>
       </c>
       <c r="L106" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4571,7 +4568,7 @@
         <v>20</v>
       </c>
       <c r="C107" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
         <v>16</v>
@@ -4598,7 +4595,7 @@
         <v>46120</v>
       </c>
       <c r="L107" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -4609,7 +4606,7 @@
         <v>20</v>
       </c>
       <c r="C108" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D108" t="s">
         <v>16</v>
@@ -4636,7 +4633,7 @@
         <v>46120</v>
       </c>
       <c r="L108" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4647,7 +4644,7 @@
         <v>20</v>
       </c>
       <c r="C109" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D109" t="s">
         <v>16</v>
@@ -4674,7 +4671,7 @@
         <v>46120</v>
       </c>
       <c r="L109" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -4685,7 +4682,7 @@
         <v>20</v>
       </c>
       <c r="C110" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D110" t="s">
         <v>16</v>
@@ -4712,7 +4709,7 @@
         <v>46120</v>
       </c>
       <c r="L110" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4723,7 +4720,7 @@
         <v>20</v>
       </c>
       <c r="C111" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D111" t="s">
         <v>16</v>
@@ -4750,7 +4747,7 @@
         <v>46120</v>
       </c>
       <c r="L111" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -4761,7 +4758,7 @@
         <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D112" t="s">
         <v>16</v>
@@ -4788,7 +4785,7 @@
         <v>46120</v>
       </c>
       <c r="L112" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -4799,7 +4796,7 @@
         <v>20</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D113" t="s">
         <v>16</v>
@@ -4826,7 +4823,7 @@
         <v>46120</v>
       </c>
       <c r="L113" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -4837,7 +4834,7 @@
         <v>20</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D114" t="s">
         <v>16</v>
@@ -4864,7 +4861,7 @@
         <v>46120</v>
       </c>
       <c r="L114" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -4875,7 +4872,7 @@
         <v>20</v>
       </c>
       <c r="C115" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D115" t="s">
         <v>16</v>
@@ -4902,7 +4899,7 @@
         <v>46120</v>
       </c>
       <c r="L115" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -4913,7 +4910,7 @@
         <v>20</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D116" t="s">
         <v>16</v>
@@ -4940,7 +4937,7 @@
         <v>46120</v>
       </c>
       <c r="L116" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -4951,7 +4948,7 @@
         <v>20</v>
       </c>
       <c r="C117" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D117" t="s">
         <v>16</v>
@@ -4978,7 +4975,7 @@
         <v>46120</v>
       </c>
       <c r="L117" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -4989,7 +4986,7 @@
         <v>20</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D118" t="s">
         <v>16</v>
@@ -5016,7 +5013,7 @@
         <v>46120</v>
       </c>
       <c r="L118" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5027,20 +5024,20 @@
         <v>20</v>
       </c>
       <c r="C119" t="s">
+        <v>25</v>
+      </c>
+      <c r="D119" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D119" t="s">
-        <v>16</v>
-      </c>
-      <c r="E119" t="s">
-        <v>16</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="H119" t="s">
         <v>16</v>
       </c>
@@ -5054,7 +5051,7 @@
         <v>46120</v>
       </c>
       <c r="L119" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -5065,20 +5062,20 @@
         <v>20</v>
       </c>
       <c r="C120" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D120" t="s">
-        <v>16</v>
-      </c>
-      <c r="E120" t="s">
-        <v>16</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="H120" t="s">
         <v>16</v>
       </c>
@@ -5092,7 +5089,7 @@
         <v>46120</v>
       </c>
       <c r="L120" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5103,7 +5100,7 @@
         <v>20</v>
       </c>
       <c r="C121" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D121" t="s">
         <v>16</v>
@@ -5130,7 +5127,7 @@
         <v>46120</v>
       </c>
       <c r="L121" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5141,7 +5138,7 @@
         <v>20</v>
       </c>
       <c r="C122" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D122" t="s">
         <v>16</v>
@@ -5168,7 +5165,7 @@
         <v>46120</v>
       </c>
       <c r="L122" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5179,7 +5176,7 @@
         <v>20</v>
       </c>
       <c r="C123" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D123" t="s">
         <v>16</v>
@@ -5206,7 +5203,7 @@
         <v>46120</v>
       </c>
       <c r="L123" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5217,20 +5214,20 @@
         <v>20</v>
       </c>
       <c r="C124" t="s">
+        <v>25</v>
+      </c>
+      <c r="D124" t="s">
+        <v>16</v>
+      </c>
+      <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D124" t="s">
-        <v>16</v>
-      </c>
-      <c r="E124" t="s">
-        <v>16</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="H124" t="s">
         <v>16</v>
       </c>
@@ -5244,7 +5241,7 @@
         <v>46120</v>
       </c>
       <c r="L124" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5255,20 +5252,20 @@
         <v>20</v>
       </c>
       <c r="C125" t="s">
+        <v>25</v>
+      </c>
+      <c r="D125" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" t="s">
+        <v>16</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D125" t="s">
-        <v>16</v>
-      </c>
-      <c r="E125" t="s">
-        <v>16</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="H125" t="s">
         <v>16</v>
       </c>
@@ -5282,7 +5279,7 @@
         <v>46120</v>
       </c>
       <c r="L125" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5293,7 +5290,7 @@
         <v>20</v>
       </c>
       <c r="C126" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D126" t="s">
         <v>16</v>
@@ -5305,7 +5302,7 @@
         <v>16</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H126" t="s">
         <v>16</v>
@@ -5320,7 +5317,7 @@
         <v>46120</v>
       </c>
       <c r="L126" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5331,7 +5328,7 @@
         <v>20</v>
       </c>
       <c r="C127" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D127" t="s">
         <v>16</v>
@@ -5343,7 +5340,7 @@
         <v>16</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H127" t="s">
         <v>16</v>
@@ -5358,7 +5355,7 @@
         <v>46120</v>
       </c>
       <c r="L127" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5369,7 +5366,7 @@
         <v>20</v>
       </c>
       <c r="C128" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D128" t="s">
         <v>16</v>
@@ -5381,7 +5378,7 @@
         <v>16</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H128" t="s">
         <v>16</v>
@@ -5396,7 +5393,7 @@
         <v>46120</v>
       </c>
       <c r="L128" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5407,7 +5404,7 @@
         <v>20</v>
       </c>
       <c r="C129" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D129" t="s">
         <v>16</v>
@@ -5419,7 +5416,7 @@
         <v>16</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H129" t="s">
         <v>16</v>
@@ -5434,7 +5431,7 @@
         <v>46120</v>
       </c>
       <c r="L129" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -5445,7 +5442,7 @@
         <v>20</v>
       </c>
       <c r="C130" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D130" t="s">
         <v>16</v>
@@ -5457,7 +5454,7 @@
         <v>16</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H130" t="s">
         <v>16</v>
@@ -5472,7 +5469,7 @@
         <v>46120</v>
       </c>
       <c r="L130" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -5483,7 +5480,7 @@
         <v>20</v>
       </c>
       <c r="C131" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D131" t="s">
         <v>16</v>
@@ -5495,7 +5492,7 @@
         <v>16</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H131" t="s">
         <v>16</v>
@@ -5510,7 +5507,7 @@
         <v>46120</v>
       </c>
       <c r="L131" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -5521,7 +5518,7 @@
         <v>20</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D132" t="s">
         <v>16</v>
@@ -5548,7 +5545,7 @@
         <v>46120</v>
       </c>
       <c r="L132" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -5559,7 +5556,7 @@
         <v>20</v>
       </c>
       <c r="C133" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D133" t="s">
         <v>16</v>
@@ -5586,7 +5583,7 @@
         <v>46120</v>
       </c>
       <c r="L133" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -5597,7 +5594,7 @@
         <v>20</v>
       </c>
       <c r="C134" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D134" t="s">
         <v>16</v>
@@ -5624,7 +5621,7 @@
         <v>46120</v>
       </c>
       <c r="L134" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:12">
